--- a/quizzes/015_korean_language_beginner_quiz--quizzes.xlsx
+++ b/quizzes/015_korean_language_beginner_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -807,8 +807,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -836,12 +836,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Beginner'}</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'multiple_choice'}</t>
+          <t>multiple_choice</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Multiple Choice'}</t>
+          <t>Multiple Choice</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'true/false'}</t>
+          <t>true/false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'True/False'}</t>
+          <t>True/False</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'short_answer'}</t>
+          <t>short_answer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Short Answer'}</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'grammar'}</t>
+          <t>grammar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Grammar'}</t>
+          <t>Grammar</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'vocabulary'}</t>
+          <t>vocabulary</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Vocabulary'}</t>
+          <t>Vocabulary</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'reading'}</t>
+          <t>reading</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Reading'}</t>
+          <t>Reading</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'1-5'}</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': '1-5'}</t>
+          <t>1-5</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'6-10'}</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': '6-10'}</t>
+          <t>6-10</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'11-15'}</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': '11-15'}</t>
+          <t>11-15</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'16-20'}</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': '16-20'}</t>
+          <t>16-20</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'21-25'}</t>
+          <t>21-25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': '21-25'}</t>
+          <t>21-25</t>
         </is>
       </c>
     </row>
